--- a/Result/profitability/3325.xlsx
+++ b/Result/profitability/3325.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.71</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2912500000000001</v>
+        <v>-0.31875</v>
       </c>
       <c r="N2" t="n">
-        <v>4.03375</v>
+        <v>0.8787500000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.20375</v>
+        <v>-0.26375</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6525</v>
+        <v>2.61125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1225</v>
+        <v>-0.16375</v>
       </c>
       <c r="N4" t="n">
-        <v>6.213749999999999</v>
+        <v>3.42125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.035</v>
+        <v>-0.09000000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>7.48125</v>
+        <v>3.955</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07124999999999999</v>
+        <v>0.02124999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.36875</v>
+        <v>4.97125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>0.16875</v>
+        <v>0.145</v>
       </c>
       <c r="N7" t="n">
-        <v>9.664999999999999</v>
+        <v>6.897500000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2825</v>
+        <v>0.26375</v>
       </c>
       <c r="N8" t="n">
-        <v>10.76375</v>
+        <v>8.94</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3325</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>137</v>
+      </c>
+      <c r="D75" t="n">
+        <v>165</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-19.92</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-71</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-51.98%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-88</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-83</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.4737500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-0.4162499999999998</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-14.59</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>2.737335834896811</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.419354838709677</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-28.21</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-3.402895054282268</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
